--- a/testdata/dataTST.xlsx
+++ b/testdata/dataTST.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="28800" windowHeight="12240"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="110">
   <si>
     <t>username</t>
   </si>
@@ -284,24 +284,27 @@
     <t>ĆEVMI DRRE</t>
   </si>
   <si>
+    <t>205-9001001626239-86</t>
+  </si>
+  <si>
+    <t>RS35 2059 0310 0000 1487 39</t>
+  </si>
+  <si>
     <t>205-9001007839862-95</t>
   </si>
   <si>
-    <t>RS35 2059 0310 0263 7397 40</t>
-  </si>
-  <si>
-    <t>205-9001001626239-86</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Visa prepaid </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  4313 **** **** 5507 </t>
+    <t>Visa Gold revolving</t>
+  </si>
+  <si>
+    <t>4176 **** **** 4784</t>
   </si>
   <si>
     <t>4313********5507</t>
   </si>
   <si>
+    <t>4313 **** **** 5507</t>
+  </si>
+  <si>
     <t xml:space="preserve"> A vista depozitni račun </t>
   </si>
   <si>
@@ -311,6 +314,21 @@
     <t>9011008661345</t>
   </si>
   <si>
+    <t>9032005130761</t>
+  </si>
+  <si>
+    <t>9032005664316</t>
+  </si>
+  <si>
+    <t>Gotovinski kredit</t>
+  </si>
+  <si>
+    <t>0049015018282</t>
+  </si>
+  <si>
+    <t>0049038646620</t>
+  </si>
+  <si>
     <t>Jail ĆEVGIMILĆ</t>
   </si>
   <si>
@@ -320,16 +338,10 @@
     <t>RS35 2059 0310 0108 6257 79</t>
   </si>
   <si>
-    <t>Visa Gold revolving</t>
-  </si>
-  <si>
     <t>4176 **** **** 4328</t>
   </si>
   <si>
     <t>4176********4328</t>
-  </si>
-  <si>
-    <t>Gotovinski kredit</t>
   </si>
   <si>
     <t>0049005001233</t>
@@ -357,13 +369,18 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -374,18 +391,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF1E1E1E"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1E1E1E"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -860,137 +865,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1001,30 +1006,27 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
@@ -1046,7 +1048,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1700,7 +1702,7 @@
       <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="10" t="s">
+      <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="1" t="s">
@@ -1762,7 +1764,7 @@
       <c r="E2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>47</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -1810,25 +1812,25 @@
       <c r="U2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="V2" s="12" t="s">
+      <c r="V2" s="11" t="s">
         <v>59</v>
       </c>
       <c r="W2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="X2" s="12" t="s">
+      <c r="X2" s="11" t="s">
         <v>61</v>
       </c>
       <c r="Y2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="Z2" s="12" t="s">
+      <c r="Z2" s="11" t="s">
         <v>63</v>
       </c>
       <c r="AA2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AB2" s="12" t="s">
+      <c r="AB2" s="11" t="s">
         <v>64</v>
       </c>
       <c r="AC2" s="2" t="s">
@@ -1880,7 +1882,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" spans="1:34">
+    <row r="3" s="3" customFormat="1" spans="1:44">
       <c r="A3" s="1" t="s">
         <v>71</v>
       </c>
@@ -1899,7 +1901,7 @@
       <c r="F3" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>73</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -1917,7 +1919,7 @@
       <c r="L3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="7" t="s">
         <v>75</v>
       </c>
       <c r="N3" s="2" t="s">
@@ -1984,7 +1986,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" s="3" customFormat="1" spans="1:34">
+    <row r="4" s="3" customFormat="1" spans="1:44">
       <c r="A4" s="1" t="s">
         <v>77</v>
       </c>
@@ -2088,7 +2090,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="15" customHeight="1" spans="1:34">
+    <row r="5" s="2" customFormat="1" ht="15" customHeight="1" spans="1:44">
       <c r="A5" s="1" t="s">
         <v>83</v>
       </c>
@@ -2098,13 +2100,13 @@
       <c r="C5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="2" t="s">
         <v>85</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -2138,10 +2140,10 @@
         <v>90</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>47</v>
@@ -2150,28 +2152,28 @@
         <v>47</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="V5" s="12" t="s">
         <v>92</v>
       </c>
+      <c r="V5" s="11" t="s">
+        <v>93</v>
+      </c>
       <c r="W5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="X5" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
+      </c>
+      <c r="X5" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>47</v>
+        <v>62</v>
+      </c>
+      <c r="Z5" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB5" s="2" t="s">
-        <v>47</v>
+        <v>62</v>
+      </c>
+      <c r="AB5" s="11" t="s">
+        <v>96</v>
       </c>
       <c r="AC5" s="2" t="s">
         <v>47</v>
@@ -2179,22 +2181,22 @@
       <c r="AD5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AE5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH5" s="2" t="s">
-        <v>47</v>
+      <c r="AE5" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF5" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG5" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH5" s="11" t="s">
+        <v>99</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:34">
-      <c r="A6" s="8" t="s">
-        <v>94</v>
+    <row r="6" s="3" customFormat="1" spans="1:44">
+      <c r="A6" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>47</v>
@@ -2209,7 +2211,7 @@
         <v>49</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>47</v>
@@ -2220,8 +2222,8 @@
       <c r="I6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>96</v>
+      <c r="J6" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>47</v>
@@ -2233,72 +2235,72 @@
         <v>47</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE6" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="X6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AD6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE6" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF6" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="AG6" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="AH6" s="13" t="s">
-        <v>102</v>
+      <c r="AF6" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="AG6" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH6" s="12" t="s">
+        <v>106</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" spans="1:34">
-      <c r="A7" s="8" t="s">
-        <v>103</v>
+    <row r="7" s="3" customFormat="1" spans="1:44">
+      <c r="A7" s="10" t="s">
+        <v>107</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>47</v>
@@ -2313,7 +2315,7 @@
         <v>49</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>47</v>
@@ -2324,8 +2326,8 @@
       <c r="I7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="4" t="s">
-        <v>105</v>
+      <c r="J7" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>47</v>
